--- a/ansible_roles_permissions_sa.xlsx
+++ b/ansible_roles_permissions_sa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vineet.thakur.ext/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vineet.thakur.ext/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19522B45-8872-E345-81F6-42B145F5EF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B8490B-7621-9943-9A8C-C2BC8C6B3942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{FD0CC9C1-5256-3947-B1B2-833F124D944B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="135">
   <si>
     <t>Custom Diagnostic ClusterRole Permissions</t>
   </si>
@@ -727,9 +727,6 @@
     <t>Node &amp; OS Configurations (MachineConfig / MCO)</t>
   </si>
   <si>
-    <t>• Custom Resource definitions for audit logging and cluster-wide event export policies</t>
-  </si>
-  <si>
     <t>Virtualization (OpenShift Virtualization / KubeVirt)</t>
   </si>
   <si>
@@ -737,178 +734,6 @@
   </si>
   <si>
     <t>Storage Operations (Portworx / Enterprise)</t>
-  </si>
-  <si>
-    <t>• Upgrade graph policies (ClusterVersion upstream channel definitions)
-• Maintenance window MachineConfigPool pause/unpause rules
-• OLM update channel definitions</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Check update paths &amp; cluster status:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc get clusterversion
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Initiate cluster upgrade:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc adm upgrade --to=&lt;version&gt;
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Monitor rollout status:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc adm upgrade status
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pause worker upgrades during maintenance:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc patch mcp/worker --type merge -p '{"spec":{"paused":true}}'</t>
-    </r>
-  </si>
-  <si>
-    <t>• NTP/chrony configurations (chrony.conf MachineConfigs)
-• System resource tuning (systemReserved, kubeReserved, evictionHard via KubeletConfig)
-• Sysctl tuning, kernel parameters, multipath settings</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Check MCO degradation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: oc get mcp
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pause MCO auto-reboots:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc patch mcp/worker --type merge -p '{"spec":{"paused":true}}'
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Force node OS reboot:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc debug node/&lt;node&gt; -- chroot /host reboot</t>
-    </r>
   </si>
   <si>
     <t>Node Maintenance – Cordon / Drain / Uncordon</t>
@@ -1058,12 +883,6 @@
     <t>Node Troubleshooting &amp; Recovery</t>
   </si>
   <si>
-    <t>• Node configuration and policies maintained through MachineConfig, KubeletConfig and GitOps</t>
-  </si>
-  <si>
-    <t>Pod / Workload Recovery</t>
-  </si>
-  <si>
     <t>• Deployment, StatefulSet, DaemonSet and configuration manifests</t>
   </si>
   <si>
@@ -1076,9 +895,6 @@
     <t>Networking Operations</t>
   </si>
   <si>
-    <t>• Network configuration, NetworkPolicy, Routes, Services and NAD manifests</t>
-  </si>
-  <si>
     <t>Operator Troubleshooting</t>
   </si>
   <si>
@@ -1091,31 +907,16 @@
     <t>• PrometheusRule, Alertmanager configuration and monitoring configuration</t>
   </si>
   <si>
-    <t>• Investigate alerts
-• Check Prometheus targets/rules
-• Check Alertmanager configuration and component health</t>
-  </si>
-  <si>
     <t>Backup / Restore</t>
   </si>
   <si>
     <t>• Velero schedules and backup/restore configuration where supported</t>
   </si>
   <si>
-    <t>• Verify backup jobs
-• Inspect Velero status
-• Perform workload restores when required</t>
-  </si>
-  <si>
     <t>Security / Access</t>
   </si>
   <si>
     <t>• RBAC, RoleBinding, NetworkPolicy and service-account configuration</t>
-  </si>
-  <si>
-    <t>• Troubleshoot RBAC permissions
-• Inspect SCC assignment
-• Investigate authentication/authorization issues</t>
   </si>
   <si>
     <t>Cluster Capacity / Scaling</t>
@@ -1125,11 +926,6 @@
 • Scaling configuration maintained through GitOps</t>
   </si>
   <si>
-    <t>• Add/remove or scale worker nodes
-• Check MachineSet and Machine API status
-• Investigate scheduling/capacity constraints</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">• </t>
     </r>
@@ -1194,52 +990,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>: pxctl volume list</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>•</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Dump targeted API states &amp; logs:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc inspect ns/&lt;namespace&gt; --dest-dir=./diag
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Inspect deployment:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> oc inspect deployment/&lt;app&gt; -n &lt;ns&gt;</t>
     </r>
   </si>
   <si>
@@ -1661,6 +1411,800 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> - oc rollout restart deployment/&lt;app&gt;
+</t>
+    </r>
+  </si>
+  <si>
+    <t>etcd operations</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check etcd cluster health</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: oc get pods -n openshift-etcd -o wide
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check etcd member status:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc rsh -n openshift-etcd etcd-&lt;node&gt; etcdctl member list
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check etcd logs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: oc logs -n openshift-etcd etcd-&lt;node&gt;
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check etcd events</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: oc get events -n openshift-etcd --sort-by=.lastTimestamp</t>
+    </r>
+  </si>
+  <si>
+    <t>Image Registry Operations</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>check registry operator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc get co image-registry
+•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Check registry pods</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: oc get pods -n openshift-image-registry -o wide
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check registry status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: oc get configs.imageregistry.operator.openshift.io cluster -o yaml
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Check registry logs: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>oc logs -n openshift-image-registry &lt;registry-pod&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Compliance Operations</t>
+  </si>
+  <si>
+    <t>Compliance profiles
+• Scan configuration
+• Remediation configuration</t>
+  </si>
+  <si>
+    <t>OpenTelemetry / Observability</t>
+  </si>
+  <si>
+    <t>• OpenTelemetryCollector configuration
+• ServiceMonitor
+• PrometheusRule
+• Alertmanager configuration</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check compliance pods:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc get pods -n openshift-compliance
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check scans:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc get compliancescan -n openshift-compliance
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check non-compliant rules:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc get compliancecheckresults -n openshift-compliance</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check collector:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc get opentelemetrycollector -A
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check collector pods</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: oc get pods -A -l app.kubernetes.io/part-of=opentelemetry
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check collector logs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: oc logs -n &lt;namespace&gt; &lt;collector-pod&gt;
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check ServiceMonitor:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc get servicemonitor -A
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Investigate alerts </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - oc get prometheusrules -A
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check Prometheus targets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - oc get alerts -A
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check Alertmanager configuration and component health -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+oc logs -n openshift-monitoring alertmanager-main-0 -c alertmanager
+oc get pods -n openshift-monitoring -l app.kubernetes.io/name=alertmanager</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>• Verify  jobs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - oc get jobs
+• Perform workload restores when required</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Troubleshoot RBAC permissions </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- oc auth can-i &lt;verb&gt; &lt;resource&gt; -n &lt;namespace&gt;
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Inspect SCC assignment. -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ oc get scc
+oc adm policy who-can use scc/&lt;scc-name&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• Investigate authentication/authorization issues- 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">oc get oauth cluster -o yaml
+oc get user &lt;username&gt; -o yaml
+oc auth can-i &lt;verb&gt; &lt;resource&gt; -n &lt;namespace&gt; --as=&lt;username&gt;
+oc get sa
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Backup and encryption management</t>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Check ClusterOperator status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - oc get operators
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Inspect CSVs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - oc get csv -A
+•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Review operator logs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - oc get pods -n &lt;operator-namespace&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check update paths &amp; cluster status:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc get clusterversion
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Initiate cluster upgrade:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc adm upgrade --to=&lt;version&gt;
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Monitor rollout status:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc adm upgrade status
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pause worker upgrades during maintenance:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc patch mcp/worker --type merge -p '{"spec":{"paused":true}}'
+•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cluster operators health: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>oc get co</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">• Upgrade graph policies (ClusterVersion upstream channel definitions)
+• Maintenance window MachineConfigPool pause/unpause rules
+• OLM update channel definitions
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• NTP/chrony configurations (chrony.conf MachineConfigs)
+• System resource tuning (systemReserved, kubeReserved, evictionHard via KubeletConfig)
+• Sysctl tuning, kernel parameters, multipath 
+</t>
+  </si>
+  <si>
+    <t>• Network configuration
+ • NetworkPolicy
+•  Routes
+• Services
+• VLAN configuration and NetworkAttachmentDefinitions (Multus) for VLAN-backed interfaces
+•  NIC bonding</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check MCO degradation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: oc get mcp
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pause MCO auto-reboots:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc patch mcp/worker --type merge -p '{"spec":{"paused":true}}'
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Force node OS reboot:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc debug node/&lt;node&gt; -- chroot /host reboot
 </t>
     </r>
   </si>
@@ -1756,6 +2300,136 @@
 oc debug node/&lt;node&gt; -- chroot /host ip route
 </t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Check VLAN/NAD configuration: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">oc get net-attach-def &lt;nad&gt; -n &lt;namespace&gt; -o yaml
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check VLAN interfaces on the node:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc debug node/&lt;node&gt; -- chroot /host ip -d link
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Check nic/bond status:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  ip a | grep bond</t>
+    </r>
+  </si>
+  <si>
+    <t>Pod / Workload configuration &amp; Recovery</t>
+  </si>
+  <si>
+    <t>• Node configuration and policies maintained through MachineConfig, KubeletConfig</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• Add/remove or scale worker nodes
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>oc get machines -A -o wide 
+oc delete machine &lt;machine-name&gt; -n &lt;machine-api-namespace&gt;
+oc scale machineset &lt;machineset-name&gt; -n &lt;machine-api-namespace&gt; --replicas=&lt;count&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>• Check MachineSet and Machine API status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+oc get machinesets -A
+oc get clusteroperator machine-api
+</t>
+    </r>
+  </si>
+  <si>
+    <t>• Custom Resource definitions for audit logging 
+• cluster-wide event export policies</t>
   </si>
   <si>
     <r>
@@ -1769,17 +2443,17 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Check ClusterOperator status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - oc get co
+      <t xml:space="preserve"> Dump targeted API states &amp; logs:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc inspect ns/&lt;namespace&gt; --dest-dir=./diag
 • </t>
     </r>
     <r>
@@ -1790,17 +2464,38 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Inspect CSVs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - oc get csv -A
+      <t>Inspect deployment:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> oc inspect deployment/&lt;app&gt; -n &lt;ns&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>• Inspect node</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: oc adm inspect node/&lt;node-name&gt; --dest-dir=./diag
 •</t>
     </r>
     <r>
@@ -1811,18 +2506,23 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Review operator logs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - oc get pods -n &lt;operator-namespace&gt;</t>
-    </r>
+      <t xml:space="preserve"> Collect events</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: oc get events -n &lt;namespace&gt; --sort-by=.lastTimestamp</t>
+    </r>
+  </si>
+  <si>
+    <t>• image Registry configuration
+• Registry storage configuration
+• Image pruning policies</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +2651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1969,6 +2669,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2437,7 +3149,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E123C3-D521-CD41-A02D-9D567B1F0245}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2458,131 +3170,131 @@
     </row>
     <row r="2" spans="1:3" ht="85" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="85" customHeight="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="98" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>75</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="85" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="85" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="118" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="85" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="85" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="112" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="85" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="85" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="149" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="196" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="85" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>122</v>
@@ -2590,46 +3302,90 @@
     </row>
     <row r="14" spans="1:3" ht="85" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="85" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="85" customHeight="1">
+        <v>97</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="152" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="123" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="68">
+      <c r="A18" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B18" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="8" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="68">
+      <c r="A19" s="10" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="85" customHeight="1">
-      <c r="A17" s="7" t="s">
+      <c r="B19" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="B17" s="8" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="51">
+      <c r="A20" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="B20" s="11" t="s">
         <v>113</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="85">
+      <c r="A21" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
